--- a/data/daily_sales.xlsx
+++ b/data/daily_sales.xlsx
@@ -918,2434 +918,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:clrMapOvr bg1="lt1" tx1="dk1" bg2="lt2" tx2="dk2" accent1="accent1" accent2="accent2" accent3="accent3" accent4="accent4" accent5="accent5" accent6="accent6" hlink="hlink" folHlink="folHlink"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr lang="zh-CN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                <a:cs typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                <a:sym typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr altLang="en-US"/>
-              <a:t>日销售额趋势分析</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>sales_analysis!$A$1:$A$252</c:f>
-              <c:numCache>
-                <c:formatCode>yyyy/m/d</c:formatCode>
-                <c:ptCount val="252"/>
-                <c:pt idx="0" c:formatCode="yyyy/m/d">
-                  <c:v>40513</c:v>
-                </c:pt>
-                <c:pt idx="1" c:formatCode="yyyy/m/d">
-                  <c:v>40514</c:v>
-                </c:pt>
-                <c:pt idx="2" c:formatCode="yyyy/m/d">
-                  <c:v>40515</c:v>
-                </c:pt>
-                <c:pt idx="3" c:formatCode="yyyy/m/d">
-                  <c:v>40517</c:v>
-                </c:pt>
-                <c:pt idx="4" c:formatCode="yyyy/m/d">
-                  <c:v>40518</c:v>
-                </c:pt>
-                <c:pt idx="5" c:formatCode="yyyy/m/d">
-                  <c:v>40519</c:v>
-                </c:pt>
-                <c:pt idx="6" c:formatCode="yyyy/m/d">
-                  <c:v>40520</c:v>
-                </c:pt>
-                <c:pt idx="7" c:formatCode="yyyy/m/d">
-                  <c:v>40521</c:v>
-                </c:pt>
-                <c:pt idx="8" c:formatCode="yyyy/m/d">
-                  <c:v>40522</c:v>
-                </c:pt>
-                <c:pt idx="9" c:formatCode="yyyy/m/d">
-                  <c:v>40524</c:v>
-                </c:pt>
-                <c:pt idx="10" c:formatCode="yyyy/m/d">
-                  <c:v>40525</c:v>
-                </c:pt>
-                <c:pt idx="11" c:formatCode="yyyy/m/d">
-                  <c:v>40526</c:v>
-                </c:pt>
-                <c:pt idx="12" c:formatCode="yyyy/m/d">
-                  <c:v>40527</c:v>
-                </c:pt>
-                <c:pt idx="13" c:formatCode="yyyy/m/d">
-                  <c:v>40528</c:v>
-                </c:pt>
-                <c:pt idx="14" c:formatCode="yyyy/m/d">
-                  <c:v>40529</c:v>
-                </c:pt>
-                <c:pt idx="15" c:formatCode="yyyy/m/d">
-                  <c:v>40548</c:v>
-                </c:pt>
-                <c:pt idx="16" c:formatCode="yyyy/m/d">
-                  <c:v>40549</c:v>
-                </c:pt>
-                <c:pt idx="17" c:formatCode="yyyy/m/d">
-                  <c:v>40550</c:v>
-                </c:pt>
-                <c:pt idx="18" c:formatCode="yyyy/m/d">
-                  <c:v>40552</c:v>
-                </c:pt>
-                <c:pt idx="19" c:formatCode="yyyy/m/d">
-                  <c:v>40553</c:v>
-                </c:pt>
-                <c:pt idx="20" c:formatCode="yyyy/m/d">
-                  <c:v>40554</c:v>
-                </c:pt>
-                <c:pt idx="21" c:formatCode="yyyy/m/d">
-                  <c:v>40555</c:v>
-                </c:pt>
-                <c:pt idx="22" c:formatCode="yyyy/m/d">
-                  <c:v>40561</c:v>
-                </c:pt>
-                <c:pt idx="23" c:formatCode="yyyy/m/d">
-                  <c:v>40562</c:v>
-                </c:pt>
-                <c:pt idx="24" c:formatCode="yyyy/m/d">
-                  <c:v>40563</c:v>
-                </c:pt>
-                <c:pt idx="25" c:formatCode="yyyy/m/d">
-                  <c:v>40564</c:v>
-                </c:pt>
-                <c:pt idx="26" c:formatCode="yyyy/m/d">
-                  <c:v>40566</c:v>
-                </c:pt>
-                <c:pt idx="27" c:formatCode="yyyy/m/d">
-                  <c:v>40567</c:v>
-                </c:pt>
-                <c:pt idx="28" c:formatCode="yyyy/m/d">
-                  <c:v>40568</c:v>
-                </c:pt>
-                <c:pt idx="29" c:formatCode="yyyy/m/d">
-                  <c:v>40569</c:v>
-                </c:pt>
-                <c:pt idx="30" c:formatCode="yyyy/m/d">
-                  <c:v>40570</c:v>
-                </c:pt>
-                <c:pt idx="31" c:formatCode="yyyy/m/d">
-                  <c:v>40571</c:v>
-                </c:pt>
-                <c:pt idx="32" c:formatCode="yyyy/m/d">
-                  <c:v>40573</c:v>
-                </c:pt>
-                <c:pt idx="33" c:formatCode="yyyy/m/d">
-                  <c:v>40574</c:v>
-                </c:pt>
-                <c:pt idx="34" c:formatCode="yyyy/m/d">
-                  <c:v>40575</c:v>
-                </c:pt>
-                <c:pt idx="35" c:formatCode="yyyy/m/d">
-                  <c:v>40576</c:v>
-                </c:pt>
-                <c:pt idx="36" c:formatCode="yyyy/m/d">
-                  <c:v>40577</c:v>
-                </c:pt>
-                <c:pt idx="37" c:formatCode="yyyy/m/d">
-                  <c:v>40578</c:v>
-                </c:pt>
-                <c:pt idx="38" c:formatCode="yyyy/m/d">
-                  <c:v>40580</c:v>
-                </c:pt>
-                <c:pt idx="39" c:formatCode="yyyy/m/d">
-                  <c:v>40581</c:v>
-                </c:pt>
-                <c:pt idx="40" c:formatCode="yyyy/m/d">
-                  <c:v>40582</c:v>
-                </c:pt>
-                <c:pt idx="41" c:formatCode="yyyy/m/d">
-                  <c:v>40583</c:v>
-                </c:pt>
-                <c:pt idx="42" c:formatCode="yyyy/m/d">
-                  <c:v>40584</c:v>
-                </c:pt>
-                <c:pt idx="43" c:formatCode="yyyy/m/d">
-                  <c:v>40585</c:v>
-                </c:pt>
-                <c:pt idx="44" c:formatCode="yyyy/m/d">
-                  <c:v>40587</c:v>
-                </c:pt>
-                <c:pt idx="45" c:formatCode="yyyy/m/d">
-                  <c:v>40588</c:v>
-                </c:pt>
-                <c:pt idx="46" c:formatCode="yyyy/m/d">
-                  <c:v>40589</c:v>
-                </c:pt>
-                <c:pt idx="47" c:formatCode="yyyy/m/d">
-                  <c:v>40594</c:v>
-                </c:pt>
-                <c:pt idx="48" c:formatCode="yyyy/m/d">
-                  <c:v>40595</c:v>
-                </c:pt>
-                <c:pt idx="49" c:formatCode="yyyy/m/d">
-                  <c:v>40596</c:v>
-                </c:pt>
-                <c:pt idx="50" c:formatCode="yyyy/m/d">
-                  <c:v>40597</c:v>
-                </c:pt>
-                <c:pt idx="51" c:formatCode="yyyy/m/d">
-                  <c:v>40598</c:v>
-                </c:pt>
-                <c:pt idx="52" c:formatCode="yyyy/m/d">
-                  <c:v>40599</c:v>
-                </c:pt>
-                <c:pt idx="53" c:formatCode="yyyy/m/d">
-                  <c:v>40601</c:v>
-                </c:pt>
-                <c:pt idx="54" c:formatCode="yyyy/m/d">
-                  <c:v>40602</c:v>
-                </c:pt>
-                <c:pt idx="55" c:formatCode="yyyy/m/d">
-                  <c:v>40603</c:v>
-                </c:pt>
-                <c:pt idx="56" c:formatCode="yyyy/m/d">
-                  <c:v>40604</c:v>
-                </c:pt>
-                <c:pt idx="57" c:formatCode="yyyy/m/d">
-                  <c:v>40605</c:v>
-                </c:pt>
-                <c:pt idx="58" c:formatCode="yyyy/m/d">
-                  <c:v>40606</c:v>
-                </c:pt>
-                <c:pt idx="59" c:formatCode="yyyy/m/d">
-                  <c:v>40608</c:v>
-                </c:pt>
-                <c:pt idx="60" c:formatCode="yyyy/m/d">
-                  <c:v>40611</c:v>
-                </c:pt>
-                <c:pt idx="61" c:formatCode="yyyy/m/d">
-                  <c:v>40612</c:v>
-                </c:pt>
-                <c:pt idx="62" c:formatCode="yyyy/m/d">
-                  <c:v>40613</c:v>
-                </c:pt>
-                <c:pt idx="63" c:formatCode="yyyy/m/d">
-                  <c:v>40615</c:v>
-                </c:pt>
-                <c:pt idx="64" c:formatCode="yyyy/m/d">
-                  <c:v>40616</c:v>
-                </c:pt>
-                <c:pt idx="65" c:formatCode="yyyy/m/d">
-                  <c:v>40617</c:v>
-                </c:pt>
-                <c:pt idx="66" c:formatCode="yyyy/m/d">
-                  <c:v>40618</c:v>
-                </c:pt>
-                <c:pt idx="67" c:formatCode="yyyy/m/d">
-                  <c:v>40619</c:v>
-                </c:pt>
-                <c:pt idx="68" c:formatCode="yyyy/m/d">
-                  <c:v>40620</c:v>
-                </c:pt>
-                <c:pt idx="69" c:formatCode="yyyy/m/d">
-                  <c:v>40622</c:v>
-                </c:pt>
-                <c:pt idx="70" c:formatCode="yyyy/m/d">
-                  <c:v>40623</c:v>
-                </c:pt>
-                <c:pt idx="71" c:formatCode="yyyy/m/d">
-                  <c:v>40624</c:v>
-                </c:pt>
-                <c:pt idx="72" c:formatCode="yyyy/m/d">
-                  <c:v>40625</c:v>
-                </c:pt>
-                <c:pt idx="73" c:formatCode="yyyy/m/d">
-                  <c:v>40626</c:v>
-                </c:pt>
-                <c:pt idx="74" c:formatCode="yyyy/m/d">
-                  <c:v>40627</c:v>
-                </c:pt>
-                <c:pt idx="75" c:formatCode="yyyy/m/d">
-                  <c:v>40629</c:v>
-                </c:pt>
-                <c:pt idx="76" c:formatCode="yyyy/m/d">
-                  <c:v>40630</c:v>
-                </c:pt>
-                <c:pt idx="77" c:formatCode="yyyy/m/d">
-                  <c:v>40631</c:v>
-                </c:pt>
-                <c:pt idx="78" c:formatCode="yyyy/m/d">
-                  <c:v>40632</c:v>
-                </c:pt>
-                <c:pt idx="79" c:formatCode="yyyy/m/d">
-                  <c:v>40633</c:v>
-                </c:pt>
-                <c:pt idx="80" c:formatCode="yyyy/m/d">
-                  <c:v>40634</c:v>
-                </c:pt>
-                <c:pt idx="81" c:formatCode="yyyy/m/d">
-                  <c:v>40636</c:v>
-                </c:pt>
-                <c:pt idx="82" c:formatCode="yyyy/m/d">
-                  <c:v>40637</c:v>
-                </c:pt>
-                <c:pt idx="83" c:formatCode="yyyy/m/d">
-                  <c:v>40641</c:v>
-                </c:pt>
-                <c:pt idx="84" c:formatCode="yyyy/m/d">
-                  <c:v>40643</c:v>
-                </c:pt>
-                <c:pt idx="85" c:formatCode="yyyy/m/d">
-                  <c:v>40644</c:v>
-                </c:pt>
-                <c:pt idx="86" c:formatCode="yyyy/m/d">
-                  <c:v>40645</c:v>
-                </c:pt>
-                <c:pt idx="87" c:formatCode="yyyy/m/d">
-                  <c:v>40646</c:v>
-                </c:pt>
-                <c:pt idx="88" c:formatCode="yyyy/m/d">
-                  <c:v>40647</c:v>
-                </c:pt>
-                <c:pt idx="89" c:formatCode="yyyy/m/d">
-                  <c:v>40648</c:v>
-                </c:pt>
-                <c:pt idx="90" c:formatCode="yyyy/m/d">
-                  <c:v>40650</c:v>
-                </c:pt>
-                <c:pt idx="91" c:formatCode="yyyy/m/d">
-                  <c:v>40651</c:v>
-                </c:pt>
-                <c:pt idx="92" c:formatCode="yyyy/m/d">
-                  <c:v>40653</c:v>
-                </c:pt>
-                <c:pt idx="93" c:formatCode="yyyy/m/d">
-                  <c:v>40654</c:v>
-                </c:pt>
-                <c:pt idx="94" c:formatCode="yyyy/m/d">
-                  <c:v>40659</c:v>
-                </c:pt>
-                <c:pt idx="95" c:formatCode="yyyy/m/d">
-                  <c:v>40660</c:v>
-                </c:pt>
-                <c:pt idx="96" c:formatCode="yyyy/m/d">
-                  <c:v>40661</c:v>
-                </c:pt>
-                <c:pt idx="97" c:formatCode="yyyy/m/d">
-                  <c:v>40664</c:v>
-                </c:pt>
-                <c:pt idx="98" c:formatCode="yyyy/m/d">
-                  <c:v>40666</c:v>
-                </c:pt>
-                <c:pt idx="99" c:formatCode="yyyy/m/d">
-                  <c:v>40667</c:v>
-                </c:pt>
-                <c:pt idx="100" c:formatCode="yyyy/m/d">
-                  <c:v>40668</c:v>
-                </c:pt>
-                <c:pt idx="101" c:formatCode="yyyy/m/d">
-                  <c:v>40671</c:v>
-                </c:pt>
-                <c:pt idx="102" c:formatCode="yyyy/m/d">
-                  <c:v>40672</c:v>
-                </c:pt>
-                <c:pt idx="103" c:formatCode="yyyy/m/d">
-                  <c:v>40673</c:v>
-                </c:pt>
-                <c:pt idx="104" c:formatCode="yyyy/m/d">
-                  <c:v>40674</c:v>
-                </c:pt>
-                <c:pt idx="105" c:formatCode="yyyy/m/d">
-                  <c:v>40675</c:v>
-                </c:pt>
-                <c:pt idx="106" c:formatCode="yyyy/m/d">
-                  <c:v>40676</c:v>
-                </c:pt>
-                <c:pt idx="107" c:formatCode="yyyy/m/d">
-                  <c:v>40678</c:v>
-                </c:pt>
-                <c:pt idx="108" c:formatCode="yyyy/m/d">
-                  <c:v>40681</c:v>
-                </c:pt>
-                <c:pt idx="109" c:formatCode="yyyy/m/d">
-                  <c:v>40682</c:v>
-                </c:pt>
-                <c:pt idx="110" c:formatCode="yyyy/m/d">
-                  <c:v>40683</c:v>
-                </c:pt>
-                <c:pt idx="111" c:formatCode="yyyy/m/d">
-                  <c:v>40685</c:v>
-                </c:pt>
-                <c:pt idx="112" c:formatCode="yyyy/m/d">
-                  <c:v>40686</c:v>
-                </c:pt>
-                <c:pt idx="113" c:formatCode="yyyy/m/d">
-                  <c:v>40687</c:v>
-                </c:pt>
-                <c:pt idx="114" c:formatCode="yyyy/m/d">
-                  <c:v>40688</c:v>
-                </c:pt>
-                <c:pt idx="115" c:formatCode="yyyy/m/d">
-                  <c:v>40689</c:v>
-                </c:pt>
-                <c:pt idx="116" c:formatCode="yyyy/m/d">
-                  <c:v>40695</c:v>
-                </c:pt>
-                <c:pt idx="117" c:formatCode="yyyy/m/d">
-                  <c:v>40696</c:v>
-                </c:pt>
-                <c:pt idx="118" c:formatCode="yyyy/m/d">
-                  <c:v>40697</c:v>
-                </c:pt>
-                <c:pt idx="119" c:formatCode="yyyy/m/d">
-                  <c:v>40699</c:v>
-                </c:pt>
-                <c:pt idx="120" c:formatCode="yyyy/m/d">
-                  <c:v>40700</c:v>
-                </c:pt>
-                <c:pt idx="121" c:formatCode="yyyy/m/d">
-                  <c:v>40701</c:v>
-                </c:pt>
-                <c:pt idx="122" c:formatCode="yyyy/m/d">
-                  <c:v>40702</c:v>
-                </c:pt>
-                <c:pt idx="123" c:formatCode="yyyy/m/d">
-                  <c:v>40703</c:v>
-                </c:pt>
-                <c:pt idx="124" c:formatCode="yyyy/m/d">
-                  <c:v>40704</c:v>
-                </c:pt>
-                <c:pt idx="125" c:formatCode="yyyy/m/d">
-                  <c:v>40706</c:v>
-                </c:pt>
-                <c:pt idx="126" c:formatCode="yyyy/m/d">
-                  <c:v>40707</c:v>
-                </c:pt>
-                <c:pt idx="127" c:formatCode="yyyy/m/d">
-                  <c:v>40708</c:v>
-                </c:pt>
-                <c:pt idx="128" c:formatCode="yyyy/m/d">
-                  <c:v>40709</c:v>
-                </c:pt>
-                <c:pt idx="129" c:formatCode="yyyy/m/d">
-                  <c:v>40710</c:v>
-                </c:pt>
-                <c:pt idx="130" c:formatCode="yyyy/m/d">
-                  <c:v>40720</c:v>
-                </c:pt>
-                <c:pt idx="131" c:formatCode="yyyy/m/d">
-                  <c:v>40721</c:v>
-                </c:pt>
-                <c:pt idx="132" c:formatCode="yyyy/m/d">
-                  <c:v>40722</c:v>
-                </c:pt>
-                <c:pt idx="133" c:formatCode="yyyy/m/d">
-                  <c:v>40723</c:v>
-                </c:pt>
-                <c:pt idx="134" c:formatCode="yyyy/m/d">
-                  <c:v>40724</c:v>
-                </c:pt>
-                <c:pt idx="135" c:formatCode="yyyy/m/d">
-                  <c:v>40729</c:v>
-                </c:pt>
-                <c:pt idx="136" c:formatCode="yyyy/m/d">
-                  <c:v>40730</c:v>
-                </c:pt>
-                <c:pt idx="137" c:formatCode="yyyy/m/d">
-                  <c:v>40731</c:v>
-                </c:pt>
-                <c:pt idx="138" c:formatCode="yyyy/m/d">
-                  <c:v>40732</c:v>
-                </c:pt>
-                <c:pt idx="139" c:formatCode="yyyy/m/d">
-                  <c:v>40734</c:v>
-                </c:pt>
-                <c:pt idx="140" c:formatCode="yyyy/m/d">
-                  <c:v>40735</c:v>
-                </c:pt>
-                <c:pt idx="141" c:formatCode="yyyy/m/d">
-                  <c:v>40736</c:v>
-                </c:pt>
-                <c:pt idx="142" c:formatCode="yyyy/m/d">
-                  <c:v>40737</c:v>
-                </c:pt>
-                <c:pt idx="143" c:formatCode="yyyy/m/d">
-                  <c:v>40738</c:v>
-                </c:pt>
-                <c:pt idx="144" c:formatCode="yyyy/m/d">
-                  <c:v>40739</c:v>
-                </c:pt>
-                <c:pt idx="145" c:formatCode="yyyy/m/d">
-                  <c:v>40741</c:v>
-                </c:pt>
-                <c:pt idx="146" c:formatCode="yyyy/m/d">
-                  <c:v>40742</c:v>
-                </c:pt>
-                <c:pt idx="147" c:formatCode="yyyy/m/d">
-                  <c:v>40743</c:v>
-                </c:pt>
-                <c:pt idx="148" c:formatCode="yyyy/m/d">
-                  <c:v>40744</c:v>
-                </c:pt>
-                <c:pt idx="149" c:formatCode="yyyy/m/d">
-                  <c:v>40745</c:v>
-                </c:pt>
-                <c:pt idx="150" c:formatCode="yyyy/m/d">
-                  <c:v>40746</c:v>
-                </c:pt>
-                <c:pt idx="151" c:formatCode="yyyy/m/d">
-                  <c:v>40748</c:v>
-                </c:pt>
-                <c:pt idx="152" c:formatCode="yyyy/m/d">
-                  <c:v>40749</c:v>
-                </c:pt>
-                <c:pt idx="153" c:formatCode="yyyy/m/d">
-                  <c:v>40750</c:v>
-                </c:pt>
-                <c:pt idx="154" c:formatCode="yyyy/m/d">
-                  <c:v>40751</c:v>
-                </c:pt>
-                <c:pt idx="155" c:formatCode="yyyy/m/d">
-                  <c:v>40767</c:v>
-                </c:pt>
-                <c:pt idx="156" c:formatCode="yyyy/m/d">
-                  <c:v>40769</c:v>
-                </c:pt>
-                <c:pt idx="157" c:formatCode="yyyy/m/d">
-                  <c:v>40770</c:v>
-                </c:pt>
-                <c:pt idx="158" c:formatCode="yyyy/m/d">
-                  <c:v>40771</c:v>
-                </c:pt>
-                <c:pt idx="159" c:formatCode="yyyy/m/d">
-                  <c:v>40772</c:v>
-                </c:pt>
-                <c:pt idx="160" c:formatCode="yyyy/m/d">
-                  <c:v>40773</c:v>
-                </c:pt>
-                <c:pt idx="161" c:formatCode="yyyy/m/d">
-                  <c:v>40774</c:v>
-                </c:pt>
-                <c:pt idx="162" c:formatCode="yyyy/m/d">
-                  <c:v>40776</c:v>
-                </c:pt>
-                <c:pt idx="163" c:formatCode="yyyy/m/d">
-                  <c:v>40777</c:v>
-                </c:pt>
-                <c:pt idx="164" c:formatCode="yyyy/m/d">
-                  <c:v>40778</c:v>
-                </c:pt>
-                <c:pt idx="165" c:formatCode="yyyy/m/d">
-                  <c:v>40779</c:v>
-                </c:pt>
-                <c:pt idx="166" c:formatCode="yyyy/m/d">
-                  <c:v>40780</c:v>
-                </c:pt>
-                <c:pt idx="167" c:formatCode="yyyy/m/d">
-                  <c:v>40781</c:v>
-                </c:pt>
-                <c:pt idx="168" c:formatCode="yyyy/m/d">
-                  <c:v>40783</c:v>
-                </c:pt>
-                <c:pt idx="169" c:formatCode="yyyy/m/d">
-                  <c:v>40790</c:v>
-                </c:pt>
-                <c:pt idx="170" c:formatCode="yyyy/m/d">
-                  <c:v>40791</c:v>
-                </c:pt>
-                <c:pt idx="171" c:formatCode="yyyy/m/d">
-                  <c:v>40792</c:v>
-                </c:pt>
-                <c:pt idx="172" c:formatCode="yyyy/m/d">
-                  <c:v>40793</c:v>
-                </c:pt>
-                <c:pt idx="173" c:formatCode="yyyy/m/d">
-                  <c:v>40794</c:v>
-                </c:pt>
-                <c:pt idx="174" c:formatCode="yyyy/m/d">
-                  <c:v>40795</c:v>
-                </c:pt>
-                <c:pt idx="175" c:formatCode="yyyy/m/d">
-                  <c:v>40797</c:v>
-                </c:pt>
-                <c:pt idx="176" c:formatCode="yyyy/m/d">
-                  <c:v>40798</c:v>
-                </c:pt>
-                <c:pt idx="177" c:formatCode="yyyy/m/d">
-                  <c:v>40799</c:v>
-                </c:pt>
-                <c:pt idx="178" c:formatCode="yyyy/m/d">
-                  <c:v>40800</c:v>
-                </c:pt>
-                <c:pt idx="179" c:formatCode="yyyy/m/d">
-                  <c:v>40801</c:v>
-                </c:pt>
-                <c:pt idx="180" c:formatCode="yyyy/m/d">
-                  <c:v>40802</c:v>
-                </c:pt>
-                <c:pt idx="181" c:formatCode="yyyy/m/d">
-                  <c:v>40804</c:v>
-                </c:pt>
-                <c:pt idx="182" c:formatCode="yyyy/m/d">
-                  <c:v>40805</c:v>
-                </c:pt>
-                <c:pt idx="183" c:formatCode="yyyy/m/d">
-                  <c:v>40806</c:v>
-                </c:pt>
-                <c:pt idx="184" c:formatCode="yyyy/m/d">
-                  <c:v>40807</c:v>
-                </c:pt>
-                <c:pt idx="185" c:formatCode="yyyy/m/d">
-                  <c:v>40808</c:v>
-                </c:pt>
-                <c:pt idx="186" c:formatCode="yyyy/m/d">
-                  <c:v>40809</c:v>
-                </c:pt>
-                <c:pt idx="187" c:formatCode="yyyy/m/d">
-                  <c:v>40811</c:v>
-                </c:pt>
-                <c:pt idx="188" c:formatCode="yyyy/m/d">
-                  <c:v>40812</c:v>
-                </c:pt>
-                <c:pt idx="189" c:formatCode="yyyy/m/d">
-                  <c:v>40813</c:v>
-                </c:pt>
-                <c:pt idx="190" c:formatCode="yyyy/m/d">
-                  <c:v>40814</c:v>
-                </c:pt>
-                <c:pt idx="191" c:formatCode="yyyy/m/d">
-                  <c:v>40815</c:v>
-                </c:pt>
-                <c:pt idx="192" c:formatCode="yyyy/m/d">
-                  <c:v>40816</c:v>
-                </c:pt>
-                <c:pt idx="193" c:formatCode="yyyy/m/d">
-                  <c:v>40818</c:v>
-                </c:pt>
-                <c:pt idx="194" c:formatCode="yyyy/m/d">
-                  <c:v>40819</c:v>
-                </c:pt>
-                <c:pt idx="195" c:formatCode="yyyy/m/d">
-                  <c:v>40820</c:v>
-                </c:pt>
-                <c:pt idx="196" c:formatCode="yyyy/m/d">
-                  <c:v>40821</c:v>
-                </c:pt>
-                <c:pt idx="197" c:formatCode="yyyy/m/d">
-                  <c:v>40822</c:v>
-                </c:pt>
-                <c:pt idx="198" c:formatCode="yyyy/m/d">
-                  <c:v>40823</c:v>
-                </c:pt>
-                <c:pt idx="199" c:formatCode="yyyy/m/d">
-                  <c:v>40825</c:v>
-                </c:pt>
-                <c:pt idx="200" c:formatCode="yyyy/m/d">
-                  <c:v>40826</c:v>
-                </c:pt>
-                <c:pt idx="201" c:formatCode="yyyy/m/d">
-                  <c:v>40827</c:v>
-                </c:pt>
-                <c:pt idx="202" c:formatCode="yyyy/m/d">
-                  <c:v>40828</c:v>
-                </c:pt>
-                <c:pt idx="203" c:formatCode="yyyy/m/d">
-                  <c:v>40829</c:v>
-                </c:pt>
-                <c:pt idx="204" c:formatCode="yyyy/m/d">
-                  <c:v>40830</c:v>
-                </c:pt>
-                <c:pt idx="205" c:formatCode="yyyy/m/d">
-                  <c:v>40832</c:v>
-                </c:pt>
-                <c:pt idx="206" c:formatCode="yyyy/m/d">
-                  <c:v>40833</c:v>
-                </c:pt>
-                <c:pt idx="207" c:formatCode="yyyy/m/d">
-                  <c:v>40834</c:v>
-                </c:pt>
-                <c:pt idx="208" c:formatCode="yyyy/m/d">
-                  <c:v>40835</c:v>
-                </c:pt>
-                <c:pt idx="209" c:formatCode="yyyy/m/d">
-                  <c:v>40836</c:v>
-                </c:pt>
-                <c:pt idx="210" c:formatCode="yyyy/m/d">
-                  <c:v>40837</c:v>
-                </c:pt>
-                <c:pt idx="211" c:formatCode="yyyy/m/d">
-                  <c:v>40839</c:v>
-                </c:pt>
-                <c:pt idx="212" c:formatCode="yyyy/m/d">
-                  <c:v>40840</c:v>
-                </c:pt>
-                <c:pt idx="213" c:formatCode="yyyy/m/d">
-                  <c:v>40841</c:v>
-                </c:pt>
-                <c:pt idx="214" c:formatCode="yyyy/m/d">
-                  <c:v>40842</c:v>
-                </c:pt>
-                <c:pt idx="215" c:formatCode="yyyy/m/d">
-                  <c:v>40843</c:v>
-                </c:pt>
-                <c:pt idx="216" c:formatCode="yyyy/m/d">
-                  <c:v>40844</c:v>
-                </c:pt>
-                <c:pt idx="217" c:formatCode="yyyy/m/d">
-                  <c:v>40846</c:v>
-                </c:pt>
-                <c:pt idx="218" c:formatCode="yyyy/m/d">
-                  <c:v>40847</c:v>
-                </c:pt>
-                <c:pt idx="219" c:formatCode="yyyy/m/d">
-                  <c:v>40849</c:v>
-                </c:pt>
-                <c:pt idx="220" c:formatCode="yyyy/m/d">
-                  <c:v>40850</c:v>
-                </c:pt>
-                <c:pt idx="221" c:formatCode="yyyy/m/d">
-                  <c:v>40851</c:v>
-                </c:pt>
-                <c:pt idx="222" c:formatCode="yyyy/m/d">
-                  <c:v>40853</c:v>
-                </c:pt>
-                <c:pt idx="223" c:formatCode="yyyy/m/d">
-                  <c:v>40854</c:v>
-                </c:pt>
-                <c:pt idx="224" c:formatCode="yyyy/m/d">
-                  <c:v>40855</c:v>
-                </c:pt>
-                <c:pt idx="225" c:formatCode="yyyy/m/d">
-                  <c:v>40856</c:v>
-                </c:pt>
-                <c:pt idx="226" c:formatCode="yyyy/m/d">
-                  <c:v>40857</c:v>
-                </c:pt>
-                <c:pt idx="227" c:formatCode="yyyy/m/d">
-                  <c:v>40858</c:v>
-                </c:pt>
-                <c:pt idx="228" c:formatCode="yyyy/m/d">
-                  <c:v>40860</c:v>
-                </c:pt>
-                <c:pt idx="229" c:formatCode="yyyy/m/d">
-                  <c:v>40861</c:v>
-                </c:pt>
-                <c:pt idx="230" c:formatCode="yyyy/m/d">
-                  <c:v>40862</c:v>
-                </c:pt>
-                <c:pt idx="231" c:formatCode="yyyy/m/d">
-                  <c:v>40863</c:v>
-                </c:pt>
-                <c:pt idx="232" c:formatCode="yyyy/m/d">
-                  <c:v>40864</c:v>
-                </c:pt>
-                <c:pt idx="233" c:formatCode="yyyy/m/d">
-                  <c:v>40865</c:v>
-                </c:pt>
-                <c:pt idx="234" c:formatCode="yyyy/m/d">
-                  <c:v>40867</c:v>
-                </c:pt>
-                <c:pt idx="235" c:formatCode="yyyy/m/d">
-                  <c:v>40868</c:v>
-                </c:pt>
-                <c:pt idx="236" c:formatCode="yyyy/m/d">
-                  <c:v>40869</c:v>
-                </c:pt>
-                <c:pt idx="237" c:formatCode="yyyy/m/d">
-                  <c:v>40870</c:v>
-                </c:pt>
-                <c:pt idx="238" c:formatCode="yyyy/m/d">
-                  <c:v>40871</c:v>
-                </c:pt>
-                <c:pt idx="239" c:formatCode="yyyy/m/d">
-                  <c:v>40872</c:v>
-                </c:pt>
-                <c:pt idx="240" c:formatCode="yyyy/m/d">
-                  <c:v>40874</c:v>
-                </c:pt>
-                <c:pt idx="241" c:formatCode="yyyy/m/d">
-                  <c:v>40875</c:v>
-                </c:pt>
-                <c:pt idx="242" c:formatCode="yyyy/m/d">
-                  <c:v>40876</c:v>
-                </c:pt>
-                <c:pt idx="243" c:formatCode="yyyy/m/d">
-                  <c:v>40877</c:v>
-                </c:pt>
-                <c:pt idx="244" c:formatCode="yyyy/m/d">
-                  <c:v>40878</c:v>
-                </c:pt>
-                <c:pt idx="245" c:formatCode="yyyy/m/d">
-                  <c:v>40879</c:v>
-                </c:pt>
-                <c:pt idx="246" c:formatCode="yyyy/m/d">
-                  <c:v>40881</c:v>
-                </c:pt>
-                <c:pt idx="247" c:formatCode="yyyy/m/d">
-                  <c:v>40882</c:v>
-                </c:pt>
-                <c:pt idx="248" c:formatCode="yyyy/m/d">
-                  <c:v>40883</c:v>
-                </c:pt>
-                <c:pt idx="249" c:formatCode="yyyy/m/d">
-                  <c:v>40884</c:v>
-                </c:pt>
-                <c:pt idx="250" c:formatCode="yyyy/m/d">
-                  <c:v>40885</c:v>
-                </c:pt>
-                <c:pt idx="251" c:formatCode="yyyy/m/d">
-                  <c:v>40886</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>sales_analysis!$B$1:$B$252</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="252"/>
-                <c:pt idx="0">
-                  <c:v>46376.49</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>47316.53</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>23921.71</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>31771.6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>31215.64</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>53795.31</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>39248.82</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>38231.9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>33650.28</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>17305.77</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>27642.68</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>29322.3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>30311.72</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>49030.08</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>13742.02</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>238.55</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>34360.19</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>23797.79</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>15778.2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>15346.83</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>60268.78</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>13273.76</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>87589.11</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>21646.78</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>15244.73</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>24279.76</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>10400.25</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>17632.37</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>24119.3</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>17490.82</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>22157.03</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>17273.5</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>6615.75</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>18818.08</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>26376.5</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>17145.23</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>22184</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>18114.31</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>3457.11</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>23415.01</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>14168.03</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>11920.78</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>14198.51</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>18599.46</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>5713.63</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>23003.99</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>10037.16</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>7070.35</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>32801.73</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>29160.48</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>19348.07</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>21472.89</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>18377.69</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>9526.5</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>15107.02</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>23631.87</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>18686.99</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>32855.05</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>17322.47</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1404.13</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>6862.05</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>24431.72</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>20896</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>4148.12</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>26009.25</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>14936.43</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>21820.66</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>32028.94</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>23398.74</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>20084.8</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>16051.05</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>19064.29</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>21578.8</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>36697.14</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>27302.75</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>9224.4</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>20005.16</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>37190.52</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>29587.42</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>25688.61</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>24586.82</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>6918.5</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>26229.31</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>12900.07</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>9913.98</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>20184.14</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>24023.96</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>24484.42</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>35702.7</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>18021.48</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>12725.5</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>13239.36</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>8211.51</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>27804.47</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>21584.41</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>23593.2</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>21323.29</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>6973.66</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>28910.41</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>27532</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>4355.55</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>3590.51</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>21624.41</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>29870.7</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>31887.7</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>59901.56</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>25885.83</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>3974.04</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>5781.7</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>31553.51</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>25489.66</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>24231.09</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>31307.49</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>32462.48</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>21884.93</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>6084.94</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>127.62</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>28104.56</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>15042.26</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>25639.54</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>16290.98</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>33908.26</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>30192.13</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>42910.38</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>58245.12</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>12472.21</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>19719.11</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>33334.47</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>45077.54</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>31852.47</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>4114.07</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>13412.2</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>30532.37</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>12570.63</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>36713.68</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>12951.2</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>22960.48</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>27893.66</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>17558.3</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>5993.87</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>20080.03</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>17948.19</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>19432.85</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>32020.91</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>11857.3</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>16958.6</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>22018.36</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>46599.08</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>27076.97</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>30394.71</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>14633.77</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>26796.92</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>19687.31</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>17293</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>93.6</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>477.05</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>5718.57</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>17243.97</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>16077.84</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>48769.64</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>54082.81</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>17339.59</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>14566.84</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>29623.18</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>22399.11</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>38617.01</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>22495.29</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>24111.64</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>2710.65</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>9131.18</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>35698.7</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>25495.82</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>21967.42</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>23188.3</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>25142.15</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>35511.67</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>27989.4</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>48162.25</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>22027.95</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>71993.67</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>23248.98</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>15745.73</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>46607.22</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>103435.81</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>38503.06</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>57869.36</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>31781.1</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>31372.66</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>29329.84</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>29274.36</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>39057.89</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>44729.37</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>40033.44</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>11582.95</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>62275.95</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>38690.2</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>74108.43</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>60387.8</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>49187.67</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>12466.81</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>43080.32</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>46436.77</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>27731.37</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>33039.18</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>32124.68</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>22010.96</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>47005.24</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>37302.4</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>37333.52</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>61064.06</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>60417.26</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>12339.16</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>39315.28</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>36235.95</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>34435.32</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>55837.14</c:v>
-                </c:pt>
-                <c:pt idx="216">
-                  <c:v>37290.57</c:v>
-                </c:pt>
-                <c:pt idx="217">
-                  <c:v>34571.23</c:v>
-                </c:pt>
-                <c:pt idx="218">
-                  <c:v>28196.75</c:v>
-                </c:pt>
-                <c:pt idx="219">
-                  <c:v>1856.64</c:v>
-                </c:pt>
-                <c:pt idx="220">
-                  <c:v>60672.11</c:v>
-                </c:pt>
-                <c:pt idx="221">
-                  <c:v>56099.24</c:v>
-                </c:pt>
-                <c:pt idx="222">
-                  <c:v>42941.34</c:v>
-                </c:pt>
-                <c:pt idx="223">
-                  <c:v>28779.24</c:v>
-                </c:pt>
-                <c:pt idx="224">
-                  <c:v>38295.12</c:v>
-                </c:pt>
-                <c:pt idx="225">
-                  <c:v>61489.18</c:v>
-                </c:pt>
-                <c:pt idx="226">
-                  <c:v>70513.29</c:v>
-                </c:pt>
-                <c:pt idx="227">
-                  <c:v>37081.37</c:v>
-                </c:pt>
-                <c:pt idx="228">
-                  <c:v>28607.78</c:v>
-                </c:pt>
-                <c:pt idx="229">
-                  <c:v>58777.71</c:v>
-                </c:pt>
-                <c:pt idx="230">
-                  <c:v>47729</c:v>
-                </c:pt>
-                <c:pt idx="231">
-                  <c:v>48439.76</c:v>
-                </c:pt>
-                <c:pt idx="232">
-                  <c:v>55885.3</c:v>
-                </c:pt>
-                <c:pt idx="233">
-                  <c:v>36751.25</c:v>
-                </c:pt>
-                <c:pt idx="234">
-                  <c:v>30190.92</c:v>
-                </c:pt>
-                <c:pt idx="235">
-                  <c:v>45333.13</c:v>
-                </c:pt>
-                <c:pt idx="236">
-                  <c:v>49664.89</c:v>
-                </c:pt>
-                <c:pt idx="237">
-                  <c:v>71979.93</c:v>
-                </c:pt>
-                <c:pt idx="238">
-                  <c:v>38579.11</c:v>
-                </c:pt>
-                <c:pt idx="239">
-                  <c:v>26674.66</c:v>
-                </c:pt>
-                <c:pt idx="240">
-                  <c:v>17300.96</c:v>
-                </c:pt>
-                <c:pt idx="241">
-                  <c:v>51831.67</c:v>
-                </c:pt>
-                <c:pt idx="242">
-                  <c:v>48851.68</c:v>
-                </c:pt>
-                <c:pt idx="243">
-                  <c:v>41481.23</c:v>
-                </c:pt>
-                <c:pt idx="244">
-                  <c:v>44533.99</c:v>
-                </c:pt>
-                <c:pt idx="245">
-                  <c:v>44713.69</c:v>
-                </c:pt>
-                <c:pt idx="246">
-                  <c:v>20375.96</c:v>
-                </c:pt>
-                <c:pt idx="247">
-                  <c:v>58202.21</c:v>
-                </c:pt>
-                <c:pt idx="248">
-                  <c:v>46144.04</c:v>
-                </c:pt>
-                <c:pt idx="249">
-                  <c:v>68340.16</c:v>
-                </c:pt>
-                <c:pt idx="250">
-                  <c:v>626.19</c:v>
-                </c:pt>
-                <c:pt idx="251">
-                  <c:v>184349.28</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="0"/>
-        <c:smooth val="0"/>
-        <c:axId val="711270935"/>
-        <c:axId val="400350537"/>
-      </c:lineChart>
-      <c:dateAx>
-        <c:axId val="711270935"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr defTabSz="914400">
-                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                    <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                    <a:cs typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                    <a:sym typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>日期</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                <a:cs typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                <a:sym typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="400350537"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="days"/>
-      </c:dateAx>
-      <c:valAx>
-        <c:axId val="400350537"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="90200"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr defTabSz="914400">
-                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                    <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                    <a:cs typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                    <a:sym typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>销售额（Sales）</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                <a:cs typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-                <a:sym typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="711270935"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr lang="zh-CN" b="0">
-          <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-          <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-          <a:cs typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-          <a:sym typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-        </a:defRPr>
-      </a:pPr>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-      <a:effectLst/>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="90200"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>17780</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>370840</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>124460</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="15" name="图表 14" descr="7b0a202020202263686172745265734964223a20223230343731343133220a7d0a"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="3827780" y="795020"/>
-        <a:ext cx="5908040" cy="2987040"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -3601,250 +1173,6 @@
 </a:theme>
 </file>
 
-<file path=xl/theme/themeOverride1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:themeOverride xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <a:clrScheme name="WPS">
-    <a:dk1>
-      <a:sysClr val="windowText" lastClr="000000"/>
-    </a:dk1>
-    <a:lt1>
-      <a:sysClr val="window" lastClr="FFFFFF"/>
-    </a:lt1>
-    <a:dk2>
-      <a:srgbClr val="44546A"/>
-    </a:dk2>
-    <a:lt2>
-      <a:srgbClr val="E7E6E6"/>
-    </a:lt2>
-    <a:accent1>
-      <a:srgbClr val="4874CB"/>
-    </a:accent1>
-    <a:accent2>
-      <a:srgbClr val="EE822F"/>
-    </a:accent2>
-    <a:accent3>
-      <a:srgbClr val="F2BA02"/>
-    </a:accent3>
-    <a:accent4>
-      <a:srgbClr val="75BD42"/>
-    </a:accent4>
-    <a:accent5>
-      <a:srgbClr val="30C0B4"/>
-    </a:accent5>
-    <a:accent6>
-      <a:srgbClr val="E54C5E"/>
-    </a:accent6>
-    <a:hlink>
-      <a:srgbClr val="0026E5"/>
-    </a:hlink>
-    <a:folHlink>
-      <a:srgbClr val="7E1FAD"/>
-    </a:folHlink>
-  </a:clrScheme>
-  <a:fontScheme name="WPS">
-    <a:majorFont>
-      <a:latin typeface="Calibri Light"/>
-      <a:ea typeface=""/>
-      <a:cs typeface=""/>
-      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-      <a:font script="Hang" typeface="맑은 고딕"/>
-      <a:font script="Hans" typeface="宋体"/>
-      <a:font script="Hant" typeface="新細明體"/>
-      <a:font script="Arab" typeface="Times New Roman"/>
-      <a:font script="Hebr" typeface="Times New Roman"/>
-      <a:font script="Thai" typeface="Tahoma"/>
-      <a:font script="Ethi" typeface="Nyala"/>
-      <a:font script="Beng" typeface="Vrinda"/>
-      <a:font script="Gujr" typeface="Shruti"/>
-      <a:font script="Khmr" typeface="MoolBoran"/>
-      <a:font script="Knda" typeface="Tunga"/>
-      <a:font script="Guru" typeface="Raavi"/>
-      <a:font script="Cans" typeface="Euphemia"/>
-      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-      <a:font script="Thaa" typeface="MV Boli"/>
-      <a:font script="Deva" typeface="Mangal"/>
-      <a:font script="Telu" typeface="Gautami"/>
-      <a:font script="Taml" typeface="Latha"/>
-      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-      <a:font script="Orya" typeface="Kalinga"/>
-      <a:font script="Mlym" typeface="Kartika"/>
-      <a:font script="Laoo" typeface="DokChampa"/>
-      <a:font script="Sinh" typeface="Iskoola Pota"/>
-      <a:font script="Mong" typeface="Mongolian Baiti"/>
-      <a:font script="Viet" typeface="Times New Roman"/>
-      <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      <a:font script="Geor" typeface="Sylfaen"/>
-    </a:majorFont>
-    <a:minorFont>
-      <a:latin typeface="Calibri"/>
-      <a:ea typeface=""/>
-      <a:cs typeface=""/>
-      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-      <a:font script="Hang" typeface="맑은 고딕"/>
-      <a:font script="Hans" typeface="宋体"/>
-      <a:font script="Hant" typeface="新細明體"/>
-      <a:font script="Arab" typeface="Arial"/>
-      <a:font script="Hebr" typeface="Arial"/>
-      <a:font script="Thai" typeface="Tahoma"/>
-      <a:font script="Ethi" typeface="Nyala"/>
-      <a:font script="Beng" typeface="Vrinda"/>
-      <a:font script="Gujr" typeface="Shruti"/>
-      <a:font script="Khmr" typeface="DaunPenh"/>
-      <a:font script="Knda" typeface="Tunga"/>
-      <a:font script="Guru" typeface="Raavi"/>
-      <a:font script="Cans" typeface="Euphemia"/>
-      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-      <a:font script="Thaa" typeface="MV Boli"/>
-      <a:font script="Deva" typeface="Mangal"/>
-      <a:font script="Telu" typeface="Gautami"/>
-      <a:font script="Taml" typeface="Latha"/>
-      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-      <a:font script="Orya" typeface="Kalinga"/>
-      <a:font script="Mlym" typeface="Kartika"/>
-      <a:font script="Laoo" typeface="DokChampa"/>
-      <a:font script="Sinh" typeface="Iskoola Pota"/>
-      <a:font script="Mong" typeface="Mongolian Baiti"/>
-      <a:font script="Viet" typeface="Arial"/>
-      <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      <a:font script="Geor" typeface="Sylfaen"/>
-    </a:minorFont>
-  </a:fontScheme>
-  <a:fmtScheme name="WPS">
-    <a:fillStyleLst>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:gradFill>
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="phClr">
-              <a:lumOff val="17500"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="phClr"/>
-          </a:gs>
-        </a:gsLst>
-        <a:lin ang="2700000" scaled="0"/>
-      </a:gradFill>
-      <a:gradFill>
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="phClr">
-              <a:hueOff val="-2520000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="phClr"/>
-          </a:gs>
-        </a:gsLst>
-        <a:lin ang="2700000" scaled="0"/>
-      </a:gradFill>
-    </a:fillStyleLst>
-    <a:lnStyleLst>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="solid"/>
-        <a:miter lim="800000"/>
-      </a:ln>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="solid"/>
-        <a:miter lim="800000"/>
-      </a:ln>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:hueOff val="-4200000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="2700000" scaled="1"/>
-        </a:gradFill>
-        <a:prstDash val="solid"/>
-        <a:miter lim="800000"/>
-      </a:ln>
-    </a:lnStyleLst>
-    <a:effectStyleLst>
-      <a:effectStyle>
-        <a:effectLst>
-          <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-            <a:schemeClr val="phClr">
-              <a:alpha val="60000"/>
-            </a:schemeClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </a:effectStyle>
-      <a:effectStyle>
-        <a:effectLst>
-          <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
-        </a:effectLst>
-      </a:effectStyle>
-      <a:effectStyle>
-        <a:effectLst>
-          <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-            <a:srgbClr val="000000">
-              <a:alpha val="63000"/>
-            </a:srgbClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </a:effectStyle>
-    </a:effectStyleLst>
-    <a:bgFillStyleLst>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:tint val="95000"/>
-          <a:satMod val="170000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:gradFill rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="phClr">
-              <a:tint val="93000"/>
-              <a:satMod val="150000"/>
-              <a:shade val="98000"/>
-              <a:lumMod val="102000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="50000">
-            <a:schemeClr val="phClr">
-              <a:tint val="98000"/>
-              <a:satMod val="130000"/>
-              <a:shade val="90000"/>
-              <a:lumMod val="103000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="phClr">
-              <a:shade val="63000"/>
-              <a:satMod val="120000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:lin ang="5400000" scaled="0"/>
-      </a:gradFill>
-    </a:bgFillStyleLst>
-  </a:fmtScheme>
-</a:themeOverride>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -5874,6 +3202,5 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>